--- a/data/availability/projects/sodic/the-estates-residences.xlsx
+++ b/data/availability/projects/sodic/the-estates-residences.xlsx
@@ -907,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7931,63 +7931,6 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>the-estates-residences</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Landscape &amp; City View</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Ready / 2027</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>5% down · 7–8 years equal installments</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
